--- a/Luban/Datas/StageEvent.xlsx
+++ b/Luban/Datas/StageEvent.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="1" r:id="Re431f7755ead4445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageEvent" sheetId="1" r:id="Rd07e6734b3a543b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -69,7 +69,7 @@
   <x:si>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF111827"/>
         <x:rFont val="宋体"/>
         <x:family val="2"/>
@@ -78,7 +78,7 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF111827"/>
         <x:rFont val="Arial"/>
         <x:family val="2"/>
@@ -87,7 +87,7 @@
     </x:r>
     <x:r>
       <x:rPr>
-        <x:sz val="10"/>
+        <x:sz val="1000"/>
         <x:color rgb="FF111827"/>
         <x:rFont val="宋体"/>
         <x:family val="2"/>
@@ -118,15 +118,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">level_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">spawn_trophy_level_02_left_003:x=-3.2,y=5.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">level_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">spawn_trophy_level_02_right_034:x=3.2,y=5.7</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -227,7 +218,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -247,6 +238,14 @@
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
     <x:cellStyle name="Normal" xfId="2"/>
@@ -254,6 +253,23 @@
     <x:cellStyle name="常规 2" xfId="1"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -406,8 +422,8 @@
   <x:sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14"/>
   <x:cols>
     <x:col min="1" max="2" width="12.3046875" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="28.3046875" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="16.3046875" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="47.779998779296875" style="1" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.670000076293945" style="1" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12.3046875" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="43.3046875" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="20.3046875" style="1" customWidth="1"/>
@@ -625,36 +641,192 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="15.5">
-      <x:c r="B12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E12">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G12" t="b">
+      <x:c r="C12" t="str">
+        <x:v>spawn_trophy_level_02_left_017:x=-3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E12" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15.5">
-      <x:c r="B13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C13" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D13" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13">
+      <x:c r="C13" t="str">
+        <x:v>spawn_trophy_level_02_right_034:x=3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E13" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G13" t="b">
+      <x:c r="F13"/>
+      <x:c r="G13" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>spawn_trophy_level_02_left_051:x=-3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>spawn_trophy_level_02_right_068:x=3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>spawn_trophy_level_02_left_085:x=-3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>spawn_trophy_level_02_right_102:x=3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F17"/>
+      <x:c r="G17" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>spawn_trophy_level_02_left_119:x=-3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>spawn_trophy_level_02_right_136:x=3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F19"/>
+      <x:c r="G19" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>spawn_trophy_level_02_left_153:x=-3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F20"/>
+      <x:c r="G20" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>spawn_trophy_level_02_right_170:x=3.2,y=5.7</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>level_02</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F21"/>
+      <x:c r="G21" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
